--- a/Test Case/Validazione/11-Lettera Vaccinazioni/CDA2_Lettera_Vaccinazioni_OK.xlsx
+++ b/Test Case/Validazione/11-Lettera Vaccinazioni/CDA2_Lettera_Vaccinazioni_OK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sites.ey.com/sites/IBM-SOGEI-Sogei-FSE2.0-GTW/Shared Documents/Sogei - FSE 2.0 - GTW/02.  Accreditamento - contributo SME per checklist/Validazione/[Accreditamento_Fornitori] - TC OK &amp; KO - 20231213/14-Lettera di Invito per Vaccinazioni/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sites.ey.com/sites/IBM-SOGEI-Sogei-FSE2.0-GTW/Shared Documents/Sogei - FSE 2.0 - GTW/02.  Accreditamento - contributo SME per checklist/Validazione/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1044" documentId="8_{A2DAC49B-4339-4364-9B87-94C6E240D5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EFB81E1-A202-42C3-A97B-B237346EA44E}"/>
+  <xr:revisionPtr revIDLastSave="1084" documentId="8_{A2DAC49B-4339-4364-9B87-94C6E240D5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8316C964-E513-48CB-A7C8-2EC5C79B3249}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{6A7A0F53-F0E3-471A-ADA0-558DB081E382}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{6A7A0F53-F0E3-471A-ADA0-558DB081E382}"/>
   </bookViews>
   <sheets>
     <sheet name="LEGENDA" sheetId="5" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="283">
   <si>
     <t>Cardinalità/Obbligatorietà da IG</t>
   </si>
@@ -127,13 +127,31 @@
     <t>Comp_Lettera_Vac_674</t>
   </si>
   <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]</t>
+  </si>
+  <si>
     <t>All'interno della sezione è possibile riportare le informazioni relative alla vaccinazione da effettuare.</t>
   </si>
   <si>
-    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.674</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.16.840.1.113883.3.1937.777.63.10.674</t>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/templateId</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/templateId/@root</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.944</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.3.1937.777.63.10.944</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/id</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@code</t>
   </si>
   <si>
     <t>Fixed: 112069-0</t>
@@ -142,22 +160,37 @@
     <t xml:space="preserve"> 112069-0</t>
   </si>
   <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@codeSystem</t>
+  </si>
+  <si>
     <t>Fixed: 2.16.840.1.113883.6.1</t>
   </si>
   <si>
     <t>2.16.840.1.113883.6.1</t>
   </si>
   <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@codeSystemName</t>
+  </si>
+  <si>
     <t>Fixed: LOINC</t>
   </si>
   <si>
     <t>LOINC</t>
   </si>
   <si>
-    <t>Fixed: Immunization invitation letter</t>
-  </si>
-  <si>
-    <t>Immunization invitation letter</t>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@displayName</t>
+  </si>
+  <si>
+    <t>Fixed: Immunization invitation letter [Text] Narrative Preventive medicine</t>
+  </si>
+  <si>
+    <t>Immunization invitation letter [Text] Narrative Preventive medicine</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/title</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/text</t>
   </si>
   <si>
     <r>
@@ -179,24 +212,648 @@
     </r>
   </si>
   <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry</t>
+  </si>
+  <si>
     <t>Appuntamento</t>
   </si>
   <si>
     <t>entry_Vacc_Appuntamento_715</t>
   </si>
   <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter</t>
+  </si>
+  <si>
+    <t>L'elemento &lt;encounter&gt; è utilizzato per descrivere un invito, già programmato o da programmare tra l’assistito e la struttura sanitaria.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/@moodCode</t>
+  </si>
+  <si>
+    <t>Fixed: APT</t>
+  </si>
+  <si>
+    <t>APT</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/effectiveTime</t>
+  </si>
+  <si>
+    <t>Il tag &lt;effectiveTime&gt; identifica l'orario previsto per l’appuntamento.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant</t>
+  </si>
+  <si>
+    <t>L'elemento &lt;participant&gt; indica la struttura sanitaria o il luogo in cui si svolgerà l'incontro clinico.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/@typecode</t>
+  </si>
+  <si>
+    <t>Fixed: LOC</t>
+  </si>
+  <si>
+    <t>LOC</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/@classcode</t>
+  </si>
+  <si>
+    <t>Fixed: SDLOC</t>
+  </si>
+  <si>
+    <t>SDLOC</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/playingEntity</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/playingEntity/name</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/country</t>
+  </si>
+  <si>
+    <t>Identifica il codice ISTAT dello stato di residenza o domicilio o indirizzo temporaneo.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/state</t>
+  </si>
+  <si>
+    <t>Identifica il codice della regione; di residenza o domicilio o indirizzo temporaneo.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/county</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifica la sigla automobilistica della provincia; di residenza o domicilio o indirizzo temporaneo. </t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/city</t>
+  </si>
+  <si>
+    <t>Identifica la descrizione del comune di residenza o domicilio o indirizzo temporaneo.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/postalCode</t>
+  </si>
+  <si>
+    <t>Identifica il CAP di residenza o domicilio o indirizzo temporaneo.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/streetAddressLine</t>
+  </si>
+  <si>
+    <t>Identifica l’indirizzo di residenza o domicilio o indirizzo temporaneo.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/censusTract</t>
+  </si>
+  <si>
+    <t>Identifica il codice ISTAT del comune di residenza o domicilio o indirizzo temporaneo.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/telecom</t>
+  </si>
+  <si>
+    <t>L'elemento &lt;telecom&gt; è un numero telefonico (Voce o Fax), un indirizzo di posta elettronica (E-mail), o altro indirizzo di una risorsa raggiungibile con un'apparecchiatura di telecomunicazione. L'indirizzo viene specificato tramite un Universal Resource Locator URL qualificato da una specifica di tempo e codici di uso che aiutano nella decisione, di quale indirizzo scegliere, per una certa ora o giorno e finalità o scopo. In modo analogo al tag &lt;addr&gt;, i numeri di telefono, codificati con il tag &lt;telecom&gt;, sono caratterizzati dall’attributo @use.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id</t>
+  </si>
+  <si>
+    <t>0…*</t>
+  </si>
+  <si>
+    <t>1…*</t>
+  </si>
+  <si>
+    <t>Riporta l'identificativo della struttura dove si svolgerà l'appuntamento.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id/@root</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id/@extension</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id/@assignedAuthorityName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship</t>
+  </si>
+  <si>
+    <t>Questo elemento descrive le istruzioni di contatto della struttura.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/@typeCode</t>
+  </si>
+  <si>
+    <t>Fixed: COMP</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/@classCode</t>
+  </si>
+  <si>
+    <t>Fixed: OBS</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/@moodCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@code</t>
+  </si>
+  <si>
+    <t>Fixed: ASSERTION</t>
+  </si>
+  <si>
+    <t>ASSERTION</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@codeSystem</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.5.4</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.5.4</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@codeSystemName</t>
+  </si>
+  <si>
+    <t>Fixed:ActCode</t>
+  </si>
+  <si>
+    <t>ActCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@displayName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malattia per cui si effettua la Vaccinazione </t>
+  </si>
+  <si>
+    <t>Act_Malattia_Vacc_678</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/@classCode</t>
+  </si>
+  <si>
+    <t>Fixed: ACT</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/@moodCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/templateId</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/templateId/@root</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.945</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.3.1937.777.63.10.945</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@code</t>
+  </si>
+  <si>
+    <t>Fixed: 112072-4</t>
+  </si>
+  <si>
+    <t>112072-4</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@codeSystem</t>
+  </si>
+  <si>
+    <t>Fixed:2.16.840.1.113883.6.1</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@codeSystemName</t>
+  </si>
+  <si>
+    <t>Fixed:LOINC</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@displayName</t>
+  </si>
+  <si>
+    <t>Fixed: Immunization letter Preventive medicine</t>
+  </si>
+  <si>
+    <t>Immunization letter Preventive medicine</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/text</t>
+  </si>
+  <si>
+    <t>L'elemento &lt;text&gt; viene utilizzato per richiamare un contenuto presente all'interno della stessa sezione del documento.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship</t>
+  </si>
+  <si>
+    <t>Lett_Vacc - Malattia (Observation)</t>
+  </si>
+  <si>
+    <t>ER_Malat_Obs_675</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/@typeCode</t>
+  </si>
+  <si>
+    <t>Fixed: RSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RSON</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/@inversionInd</t>
+  </si>
+  <si>
+    <t>Fixed: false</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation</t>
+  </si>
+  <si>
+    <t>Elemento atto ad indicare la Malattia per la quale è prevista la vaccinazione</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/@classCode</t>
+  </si>
+  <si>
+    <t>OBS</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/@moodCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/templateId</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/templateId/@root</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.675</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.3.1937.777.63.10.675</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@code</t>
+  </si>
+  <si>
+    <t>Fixed: 75323-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 75323-6</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@codeSystem</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@codeSystemName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@displayName</t>
+  </si>
+  <si>
+    <t>Fixed: Condizione</t>
+  </si>
+  <si>
+    <t>Condizione</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@xsi:type</t>
+  </si>
+  <si>
+    <t>Fixed: CD</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@codeSystem</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.6.103</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.16.840.1.113883.6.103</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@codeSystemName</t>
+  </si>
+  <si>
+    <t>Fixed: ICD-9-CM</t>
+  </si>
+  <si>
+    <t>ICD-9-CM</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@displayName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship</t>
+  </si>
+  <si>
+    <t>Numero di Dose</t>
+  </si>
+  <si>
+    <t>ER_Num_Dose_672</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/@typeCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/@inversionInd</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation</t>
+  </si>
+  <si>
+    <t>Elemento atto ad indicare il valore numerico progressivo che identifica la dose da somministrare.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/@classCode</t>
+  </si>
+  <si>
+    <t>Fixed:OBS</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/@moodCode</t>
+  </si>
+  <si>
+    <t>Fixed:EVN</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/templateId</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/templateId/@root</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.672</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@code</t>
+  </si>
+  <si>
+    <t>Fixed: 30973-2</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@codeSystem</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@codeSystemName</t>
+  </si>
+  <si>
+    <t> Fixed: LOINC</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@displayName</t>
+  </si>
+  <si>
+    <t> Fixed: Numero di Dose</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/value</t>
+  </si>
+  <si>
+    <t>Rappresenta il numero relativo al richiamo</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/value/@xsi:type</t>
+  </si>
+  <si>
+    <t>Fixed: INT</t>
+  </si>
+  <si>
+    <t>Sezione Riferimento ad invito precedente</t>
+  </si>
+  <si>
+    <t>Comp_Rif_Inv_Prec_680</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/@typeCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/templateId</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/templateId/@root</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.680</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/Id</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@code</t>
+  </si>
+  <si>
+    <t>Fixed: 55107-7</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@codeSystem</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@codeSystemName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@displayName</t>
+  </si>
+  <si>
+    <t>Fixed: Extenal Documents</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/title</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/text</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry</t>
+  </si>
+  <si>
+    <t>Act riferimento a invito precedente</t>
+  </si>
+  <si>
+    <t>Elemento che consente di rappresentare in modo strutturato le informazioni di dettaglio riferite nel blocco narrativo. Questo elemento si riferisce a un invito precedente alla vaccinazione.</t>
+  </si>
+  <si>
+    <t>Act_Rif_Prec_679</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/@typeCode</t>
+  </si>
+  <si>
     <t>Default value is COMP</t>
   </si>
   <si>
-    <t>COMP</t>
-  </si>
-  <si>
-    <t>L'elemento &lt;encounter&gt; è utilizzato per descrivere un invito, già programmato o da programmare tra l’assistito e la struttura sanitaria.</t>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/@moodCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/@classCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/templateId</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/templateId/@root</t>
+  </si>
+  <si>
+    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.679</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@codeSystem</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@codeSystemName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@displayName</t>
+  </si>
+  <si>
+    <r>
+      <t>Fixed: Exte</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rnal documents</t>
+    </r>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/@typeCode</t>
+  </si>
+  <si>
+    <t>Fixed: REFR</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument</t>
+  </si>
+  <si>
+    <t>Elemento utilizzato per rappresentare un documento clinico correlato al documento corrente. Contiene informazioni identificative come l'ID del documento, il tipo di documento (codificato secondo uno standard, ad esempio LOINC), e stabilisce un collegamento informativo tramite una relazione di riferimento.</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/@classCode</t>
+  </si>
+  <si>
+    <t>Fixed: DOCCLIN</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/@moodCode</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id/@root</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id/@extension</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id/@assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@code</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@codeSystem</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@codeSystemName</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@displayName</t>
+  </si>
+  <si>
+    <t>Cardinalità per Test case 2</t>
+  </si>
+  <si>
+    <t>Obbligatorietà per Test case 2</t>
   </si>
   <si>
     <t xml:space="preserve">	
 Con data e ora già fissate, l’attributo @moodCode DEVE essere valorizzato con "APT".
 Se non è presente data e ora l'attributo @moodCode DEVE essere valorizzato con "RQO".</t>
+  </si>
+  <si>
+    <t>APT | RQO</t>
   </si>
   <si>
     <r>
@@ -214,307 +871,16 @@
     </r>
   </si>
   <si>
-    <t>L'elemento &lt;participant&gt; indica la struttura sanitaria o il luogo in cui si svolgerà l'incontro clinico.</t>
-  </si>
-  <si>
-    <t>Fixed: LOC</t>
-  </si>
-  <si>
-    <t>LOC</t>
-  </si>
-  <si>
-    <t>Fixed: SDLOC</t>
-  </si>
-  <si>
-    <t>SDLOC</t>
-  </si>
-  <si>
-    <t>Identifica il codice ISTAT dello stato di residenza o domicilio o indirizzo temporaneo.</t>
-  </si>
-  <si>
-    <t>Identifica il codice della regione; di residenza o domicilio o indirizzo temporaneo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifica la sigla automobilistica della provincia; di residenza o domicilio o indirizzo temporaneo. </t>
-  </si>
-  <si>
-    <t>Identifica la descrizione del comune di residenza o domicilio o indirizzo temporaneo.</t>
-  </si>
-  <si>
-    <t>Identifica il CAP di residenza o domicilio o indirizzo temporaneo.</t>
-  </si>
-  <si>
-    <t>Identifica l’indirizzo di residenza o domicilio o indirizzo temporaneo.</t>
-  </si>
-  <si>
-    <t>Identifica il codice ISTAT del comune di residenza o domicilio o indirizzo temporaneo.</t>
-  </si>
-  <si>
-    <t>L'elemento &lt;telecom&gt; è un numero telefonico (Voce o Fax), un indirizzo di posta elettronica (E-mail), o altro indirizzo di una risorsa raggiungibile con un'apparecchiatura di telecomunicazione. L'indirizzo viene specificato tramite un Universal Resource Locator URL qualificato da una specifica di tempo e codici di uso che aiutano nella decisione, di quale indirizzo scegliere, per una certa ora o giorno e finalità o scopo. In modo analogo al tag &lt;addr&gt;, i numeri di telefono, codificati con il tag &lt;telecom&gt;, sono caratterizzati dall’attributo @use.</t>
-  </si>
-  <si>
-    <t>0…*</t>
-  </si>
-  <si>
-    <t>1…*</t>
-  </si>
-  <si>
-    <t>Riporta l'identificativo della struttura dove si svolgerà l'appuntamento.</t>
-  </si>
-  <si>
-    <t>Questo elemento descrive le istruzioni di contatto della struttura.</t>
-  </si>
-  <si>
-    <t>Fixed: COMP</t>
-  </si>
-  <si>
-    <t>Fixed: OBS</t>
-  </si>
-  <si>
-    <t>OBS</t>
-  </si>
-  <si>
-    <t>Fixed: ASSERTION</t>
-  </si>
-  <si>
-    <t>ASSERTION</t>
-  </si>
-  <si>
-    <t>Fixed: 2.16.840.1.113883.5.4</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malattia per cui si effettua la Vaccinazione </t>
-  </si>
-  <si>
-    <t>Act_Malattia_Vacc_678</t>
-  </si>
-  <si>
-    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.678</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.63.10.678</t>
-  </si>
-  <si>
-    <t>Fixed:112074-2</t>
-  </si>
-  <si>
-    <t>112074-2</t>
-  </si>
-  <si>
-    <t>Fixed:2.16.840.1.113883.6.1</t>
-  </si>
-  <si>
-    <t>Fixed:LOINC</t>
-  </si>
-  <si>
-    <t>Fixed:Immunization letter</t>
-  </si>
-  <si>
-    <t>Immunization letter</t>
-  </si>
-  <si>
-    <t>L'elemento &lt;text&gt; viene utilizzato per richiamare un contenuto presente all'interno della stessa sezione del documento.</t>
+    <t>Fixed:COMP</t>
+  </si>
+  <si>
+    <t>Fixed:ASSERTION</t>
+  </si>
+  <si>
+    <t>Fixed:  2.16.840.1.113883.5.4</t>
   </si>
   <si>
     <t>Elemento atto a riportare la malattia per cui si effettua la vaccinazione.</t>
-  </si>
-  <si>
-    <t>Lett_Vacc - Malattia (Observation)</t>
-  </si>
-  <si>
-    <t>ER_Malat_Obs_675</t>
-  </si>
-  <si>
-    <t>Fixed: RSON</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RSON</t>
-  </si>
-  <si>
-    <t>Fixed: false</t>
-  </si>
-  <si>
-    <t>Elemento atto ad indicare la Malattia per la quale è prevista la vaccinazione</t>
-  </si>
-  <si>
-    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.675</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.63.10.675</t>
-  </si>
-  <si>
-    <t>Fixed: 75323-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 75323-6</t>
-  </si>
-  <si>
-    <t>Fixed: Condizione</t>
-  </si>
-  <si>
-    <t>Condizione</t>
-  </si>
-  <si>
-    <t>Fixed: CD</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
-    <t>Fixed: 2.16.840.1.113883.6.103</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.16.840.1.113883.6.103</t>
-  </si>
-  <si>
-    <t>Fixed: ICD-9-CM</t>
-  </si>
-  <si>
-    <t>ICD-9-CM</t>
-  </si>
-  <si>
-    <t>Numero di Dose</t>
-  </si>
-  <si>
-    <t>ER_Num_Dose_672</t>
-  </si>
-  <si>
-    <t>RSON</t>
-  </si>
-  <si>
-    <t>Elemento atto ad indicare il valore numerico progressivo che identifica la dose da somministrare.</t>
-  </si>
-  <si>
-    <t>Fixed:OBS</t>
-  </si>
-  <si>
-    <t>Fixed:EVN</t>
-  </si>
-  <si>
-    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.672</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.63.10.672</t>
-  </si>
-  <si>
-    <t>Fixed: 30973-2</t>
-  </si>
-  <si>
-    <t>30973-2</t>
-  </si>
-  <si>
-    <t> Fixed: LOINC</t>
-  </si>
-  <si>
-    <t> Fixed: Numero di Dose</t>
-  </si>
-  <si>
-    <t>Rappresenta il numero relativo al richiamo</t>
-  </si>
-  <si>
-    <t>Fixed: INT</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>Sezione Riferimento ad invito precedente</t>
-  </si>
-  <si>
-    <t>Comp_Rif_Inv_Prec_680</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/@typeCode</t>
-  </si>
-  <si>
-    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.680</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.63.10.680</t>
-  </si>
-  <si>
-    <t>Fixed: 55107-7</t>
-  </si>
-  <si>
-    <t>55107-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2.16.840.1.113883.6.1</t>
-  </si>
-  <si>
-    <t>Fixed: Extenal Documents</t>
-  </si>
-  <si>
-    <t>Act riferimento a invito precedente</t>
-  </si>
-  <si>
-    <t>Elemento che consente di rappresentare in modo strutturato le informazioni di dettaglio riferite nel blocco narrativo. Questo elemento si riferisce a un invito precedente alla vaccinazione.</t>
-  </si>
-  <si>
-    <t>Act_Rif_Prec_679</t>
-  </si>
-  <si>
-    <t>Fixed: ACT</t>
-  </si>
-  <si>
-    <t>ACT</t>
-  </si>
-  <si>
-    <t>Fixed: 2.16.840.1.113883.3.1937.777.63.10.679</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.3.1937.777.63.10.679</t>
-  </si>
-  <si>
-    <r>
-      <t>Fixed: Exte</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>rnal documents</t>
-    </r>
-  </si>
-  <si>
-    <t>Fixed: REFR</t>
-  </si>
-  <si>
-    <t>REFR</t>
-  </si>
-  <si>
-    <t>Elemento utilizzato per rappresentare un documento clinico correlato al documento corrente. Contiene informazioni identificative come l'ID del documento, il tipo di documento (codificato secondo uno standard, ad esempio LOINC), e stabilisce un collegamento informativo tramite una relazione di riferimento.</t>
-  </si>
-  <si>
-    <t>Fixed: DOCCLIN</t>
-  </si>
-  <si>
-    <t>DOCCLIN</t>
-  </si>
-  <si>
-    <t>Cardinalità per Test case 2</t>
-  </si>
-  <si>
-    <t>Obbligatorietà per Test case 2</t>
-  </si>
-  <si>
-    <t>Fixed:COMP</t>
-  </si>
-  <si>
-    <t>Fixed:ASSERTION</t>
-  </si>
-  <si>
-    <t>Fixed:  2.16.840.1.113883.5.4</t>
-  </si>
-  <si>
-    <t>Fixed:2.16.840.1.113883.3.1937.777.63.10.678</t>
   </si>
   <si>
     <t>Fixed:RSON</t>
@@ -538,7 +904,31 @@
     </r>
   </si>
   <si>
+    <t>RSON</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.3.1937.777.63.10.672</t>
+  </si>
+  <si>
+    <t>30973-2</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
     <t>Fixed:2.16.840.1.113883.3.1937.777.63.10.680</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.3.1937.777.63.10.680</t>
+  </si>
+  <si>
+    <t>55107-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.16.840.1.113883.6.1</t>
   </si>
   <si>
     <r>
@@ -556,416 +946,23 @@
     </r>
   </si>
   <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/templateId</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/templateId/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/id</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/code/@displayName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/title</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/text</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/@moodCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/effectiveTime</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/@typecode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/@classcode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/playingEntity</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/playingEntity/name</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/country</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/state</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/county</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/city</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/postalCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/streetAddressLine</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/addr/censusTract</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/telecom</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id/@extension</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/participant/participantRole/id/@assignedAuthorityName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/@typeCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/@classCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/@moodCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/text</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/@moodCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/@classCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/templateId</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/templateId/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/code/@displayName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/text</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/@typeCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/@inversionInd</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/@classCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/@moodCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/templateId</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/templateId/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/code/@displayName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@displayName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/@typeCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/@classCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/@moodCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/templateId</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/templateId/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/code/@displayName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/value</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/observation/value/@xsi:type</t>
-  </si>
-  <si>
-    <t>Fixed: APT</t>
-  </si>
-  <si>
-    <t>APT</t>
-  </si>
-  <si>
-    <t>Il tag &lt;effectiveTime&gt; identifica l'orario previsto per l’appuntamento.</t>
-  </si>
-  <si>
-    <t>APT | RQO</t>
-  </si>
-  <si>
-    <t>Fixed:ActCode</t>
-  </si>
-  <si>
-    <t>ActCode</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/value/@xsi:type</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/templateId</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/templateId/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/Id</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/code/@displayName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/title</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/text</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/@typeCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/@moodCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/@classCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/templateId</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/templateId/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/code/@displayName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/@typeCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/@classCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/@moodCode</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id/@root</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id/@extension</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/id/@assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Riferimento_invito_precedente]/entry/act/reference/externalDocument/code/@displayName</t>
-  </si>
-  <si>
     <t>External Documents</t>
   </si>
   <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/act/entryRelationship/observation/entryRelationship/@inversionInd</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@code</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@codeSystem</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@codeSystemName</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/component/structuredBody/component/section[@ID=Vaccinazione]/entry/encounter/entryRelationship/observation/code/@displayName</t>
+    <t>2.16.840.1.113883.3.1937.777.63.10.679</t>
+  </si>
+  <si>
+    <t>REFR</t>
+  </si>
+  <si>
+    <t>DOCCLIN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,10 +1414,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1739,13 +1732,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6B67C7-8C28-4876-9415-700A93223AD1}">
   <dimension ref="B1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="38.44140625" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:9" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="15" thickBot="1"/>
+    <row r="2" spans="2:9" ht="13.9" customHeight="1">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -1759,7 +1752,7 @@
       <c r="H2" s="29"/>
       <c r="I2" s="30"/>
     </row>
-    <row r="3" spans="2:9" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:9" ht="13.9" customHeight="1" thickBot="1">
       <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
@@ -1785,19 +1778,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B112A30-457A-4B3B-9991-ABAE6E991EB2}">
   <dimension ref="A1:I135"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="115" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" style="27" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" style="27" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" customWidth="1"/>
     <col min="6" max="6" width="52" customWidth="1"/>
-    <col min="7" max="8" width="50.6640625" customWidth="1"/>
-    <col min="9" max="9" width="24.44140625" customWidth="1"/>
+    <col min="7" max="8" width="50.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="42" customHeight="1" thickBot="1">
       <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
@@ -1826,7 +1819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="50.45" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1847,7 +1840,7 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
     </row>
-    <row r="3" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="50.45" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -1872,7 +1865,7 @@
       </c>
       <c r="I3" s="13"/>
     </row>
-    <row r="4" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="50.45" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -1897,7 +1890,7 @@
       </c>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="50.45" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1922,9 +1915,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="50.45" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>14</v>
@@ -1939,7 +1932,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="13"/>
@@ -1947,9 +1940,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="50.45" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>14</v>
@@ -1970,9 +1963,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="50.45" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>151</v>
+        <v>30</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>14</v>
@@ -1988,18 +1981,18 @@
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="50.45" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>17</v>
@@ -2020,9 +2013,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="50.45" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>14</v>
@@ -2043,9 +2036,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="50.45" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>14</v>
@@ -2061,18 +2054,18 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="50.45" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>14</v>
@@ -2088,18 +2081,18 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="50.45" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>17</v>
@@ -2115,18 +2108,18 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="50.45" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>17</v>
@@ -2142,18 +2135,18 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="50.45" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>17</v>
@@ -2174,9 +2167,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="133.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="133.9" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>14</v>
@@ -2191,7 +2184,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="14"/>
@@ -2199,9 +2192,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="50.45" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>17</v>
@@ -2216,17 +2209,17 @@
         <v>15</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="14"/>
       <c r="I17" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="50.45" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>14</v>
@@ -2241,17 +2234,17 @@
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="18"/>
       <c r="I18" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="50.45" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>162</v>
+        <v>55</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>14</v>
@@ -2267,18 +2260,18 @@
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="70.150000000000006" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>14</v>
@@ -2293,17 +2286,17 @@
         <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="18"/>
       <c r="I20" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="50.45" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="B21" s="25" t="s">
         <v>17</v>
@@ -2318,17 +2311,17 @@
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="18"/>
       <c r="I21" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="50.45" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>17</v>
@@ -2344,18 +2337,18 @@
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="50.45" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>14</v>
@@ -2373,12 +2366,12 @@
       <c r="G23" s="1"/>
       <c r="H23" s="14"/>
       <c r="I23" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="50.45" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="B24" s="25" t="s">
         <v>17</v>
@@ -2394,18 +2387,18 @@
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="50.45" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>14</v>
@@ -2423,12 +2416,12 @@
       <c r="G25" s="1"/>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="50.45" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="B26" s="25" t="s">
         <v>14</v>
@@ -2446,12 +2439,12 @@
       <c r="G26" s="1"/>
       <c r="H26" s="14"/>
       <c r="I26" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="50.45" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="B27" s="25" t="s">
         <v>17</v>
@@ -2468,12 +2461,12 @@
       <c r="G27" s="23"/>
       <c r="H27" s="19"/>
       <c r="I27" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="50.45" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="B28" s="25" t="s">
         <v>14</v>
@@ -2488,17 +2481,17 @@
         <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="14"/>
       <c r="I28" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="50.45" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="B29" s="25" t="s">
         <v>17</v>
@@ -2513,17 +2506,17 @@
         <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="14"/>
       <c r="I29" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="50.45" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="B30" s="25" t="s">
         <v>17</v>
@@ -2538,17 +2531,17 @@
         <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="14"/>
       <c r="I30" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="50.45" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="B31" s="25" t="s">
         <v>14</v>
@@ -2563,17 +2556,17 @@
         <v>15</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="14"/>
       <c r="I31" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="50.45" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="B32" s="25" t="s">
         <v>17</v>
@@ -2588,17 +2581,17 @@
         <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="14"/>
       <c r="I32" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="50.45" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>14</v>
@@ -2613,17 +2606,17 @@
         <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="14"/>
       <c r="I33" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="50.45" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="B34" s="25" t="s">
         <v>17</v>
@@ -2638,17 +2631,17 @@
         <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="14"/>
       <c r="I34" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="145.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="145.9" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>17</v>
@@ -2663,42 +2656,42 @@
         <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="14"/>
       <c r="I35" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="50.45" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C36" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="14"/>
       <c r="I36" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="50.45" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="B37" s="25" t="s">
         <v>14</v>
@@ -2716,12 +2709,12 @@
       <c r="G37" s="1"/>
       <c r="H37" s="14"/>
       <c r="I37" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="50.45" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>181</v>
+        <v>93</v>
       </c>
       <c r="B38" s="25" t="s">
         <v>14</v>
@@ -2739,12 +2732,12 @@
       <c r="G38" s="1"/>
       <c r="H38" s="14"/>
       <c r="I38" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="50.45" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>17</v>
@@ -2762,12 +2755,12 @@
       <c r="G39" s="1"/>
       <c r="H39" s="14"/>
       <c r="I39" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="50.45" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>183</v>
+        <v>95</v>
       </c>
       <c r="B40" s="25" t="s">
         <v>17</v>
@@ -2782,17 +2775,17 @@
         <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="20"/>
       <c r="I40" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="50.45" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="B41" s="25" t="s">
         <v>17</v>
@@ -2808,16 +2801,16 @@
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="50.45" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="B42" s="25" t="s">
         <v>14</v>
@@ -2835,12 +2828,12 @@
       <c r="G42" s="1"/>
       <c r="H42" s="14"/>
       <c r="I42" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="50.45" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="B43" s="25" t="s">
         <v>17</v>
@@ -2856,16 +2849,16 @@
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="50.45" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="B44" s="25" t="s">
         <v>14</v>
@@ -2887,12 +2880,12 @@
         <v>23</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="50.45" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="B45" s="25" t="s">
         <v>14</v>
@@ -2910,12 +2903,12 @@
       <c r="G45" s="1"/>
       <c r="H45" s="14"/>
       <c r="I45" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="50.45" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>280</v>
+        <v>104</v>
       </c>
       <c r="B46" s="25" t="s">
         <v>14</v>
@@ -2931,18 +2924,18 @@
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="50.45" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="B47" s="25" t="s">
         <v>14</v>
@@ -2958,18 +2951,18 @@
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="50.45" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="B48" s="25" t="s">
         <v>17</v>
@@ -2985,18 +2978,18 @@
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="50.45" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>283</v>
+        <v>113</v>
       </c>
       <c r="B49" s="25" t="s">
         <v>17</v>
@@ -3014,12 +3007,12 @@
       <c r="G49" s="1"/>
       <c r="H49" s="14"/>
       <c r="I49" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="50.45" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="B50" s="25" t="s">
         <v>17</v>
@@ -3037,36 +3030,36 @@
       <c r="G50" s="1"/>
       <c r="H50" s="14"/>
       <c r="I50" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="95.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="95.45" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C51" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="H51" s="14"/>
       <c r="I51" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="50.45" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="B52" s="25" t="s">
         <v>14</v>
@@ -3084,12 +3077,12 @@
       <c r="G52" s="1"/>
       <c r="H52" s="14"/>
       <c r="I52" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="50.45" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="B53" s="25" t="s">
         <v>14</v>
@@ -3105,18 +3098,18 @@
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="50.45" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="B54" s="25" t="s">
         <v>14</v>
@@ -3138,12 +3131,12 @@
         <v>23</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="50.45" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="B55" s="25" t="s">
         <v>17</v>
@@ -3161,12 +3154,12 @@
       <c r="G55" s="1"/>
       <c r="H55" s="15"/>
       <c r="I55" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="50.45" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="B56" s="25" t="s">
         <v>14</v>
@@ -3182,18 +3175,18 @@
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="50.45" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="B57" s="25" t="s">
         <v>17</v>
@@ -3211,12 +3204,12 @@
       <c r="G57" s="1"/>
       <c r="H57" s="13"/>
       <c r="I57" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="50.45" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>196</v>
+        <v>127</v>
       </c>
       <c r="B58" s="25" t="s">
         <v>17</v>
@@ -3232,18 +3225,18 @@
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="50.45" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="B59" s="25" t="s">
         <v>17</v>
@@ -3259,18 +3252,18 @@
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="50.45" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="B60" s="25" t="s">
         <v>17</v>
@@ -3286,18 +3279,18 @@
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="50.45" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="B61" s="25" t="s">
         <v>17</v>
@@ -3313,18 +3306,18 @@
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="50.45" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="B62" s="25" t="s">
         <v>14</v>
@@ -3339,41 +3332,41 @@
         <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="14"/>
       <c r="I62" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="50.45" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C63" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="50.45" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="B64" s="25" t="s">
         <v>14</v>
@@ -3389,18 +3382,18 @@
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="50.45" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="B65" s="25" t="s">
         <v>14</v>
@@ -3416,18 +3409,18 @@
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="50.45" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="B66" s="25" t="s">
         <v>14</v>
@@ -3442,17 +3435,17 @@
         <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="14"/>
       <c r="I66" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="50.45" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>17</v>
@@ -3468,18 +3461,18 @@
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="50.45" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="B68" s="25" t="s">
         <v>14</v>
@@ -3501,12 +3494,12 @@
         <v>23</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="50.45" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="B69" s="25" t="s">
         <v>14</v>
@@ -3524,12 +3517,12 @@
       <c r="G69" s="1"/>
       <c r="H69" s="17"/>
       <c r="I69" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="50.45" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="B70" s="25" t="s">
         <v>14</v>
@@ -3545,18 +3538,18 @@
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="50.45" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="B71" s="25" t="s">
         <v>14</v>
@@ -3574,12 +3567,12 @@
       <c r="G71" s="1"/>
       <c r="H71" s="15"/>
       <c r="I71" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="50.45" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="B72" s="25" t="s">
         <v>14</v>
@@ -3595,18 +3588,18 @@
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="50.45" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="B73" s="25" t="s">
         <v>14</v>
@@ -3622,18 +3615,18 @@
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="50.45" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="B74" s="25" t="s">
         <v>17</v>
@@ -3649,18 +3642,18 @@
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="50.45" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="B75" s="25" t="s">
         <v>17</v>
@@ -3676,18 +3669,18 @@
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="H75" s="14" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="50.45" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="B76" s="25" t="s">
         <v>14</v>
@@ -3705,12 +3698,12 @@
       <c r="G76" s="1"/>
       <c r="H76" s="16"/>
       <c r="I76" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="50.45" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>240</v>
+        <v>167</v>
       </c>
       <c r="B77" s="25" t="s">
         <v>14</v>
@@ -3726,18 +3719,18 @@
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="H77" s="14" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="50.45" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="B78" s="25" t="s">
         <v>14</v>
@@ -3755,12 +3748,12 @@
       <c r="G78" s="1"/>
       <c r="H78" s="14"/>
       <c r="I78" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="50.45" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="B79" s="25" t="s">
         <v>14</v>
@@ -3776,18 +3769,18 @@
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="H79" s="14" t="s">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="50.45" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>17</v>
@@ -3803,18 +3796,18 @@
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="50.45" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="B81" s="25" t="s">
         <v>17</v>
@@ -3832,12 +3825,12 @@
       <c r="G81" s="1"/>
       <c r="H81" s="14"/>
       <c r="I81" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="50.45" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="B82" s="25" t="s">
         <v>17</v>
@@ -3852,17 +3845,17 @@
         <v>18</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="22"/>
       <c r="I82" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="50.45" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="B83" s="25" t="s">
         <v>14</v>
@@ -3878,16 +3871,16 @@
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H83" s="14"/>
       <c r="I83" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="50.45" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>279</v>
+        <v>182</v>
       </c>
       <c r="B84" s="25" t="s">
         <v>14</v>
@@ -3903,16 +3896,16 @@
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="H84" s="14"/>
       <c r="I84" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="50.45" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="B85" s="25" t="s">
         <v>14</v>
@@ -3927,17 +3920,17 @@
         <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="14"/>
       <c r="I85" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="50.45" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="B86" s="25" t="s">
         <v>17</v>
@@ -3953,16 +3946,16 @@
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H86" s="14"/>
       <c r="I86" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="50.45" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="B87" s="25" t="s">
         <v>14</v>
@@ -3978,16 +3971,16 @@
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="H87" s="14"/>
       <c r="I87" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="50.45" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B88" s="25" t="s">
         <v>14</v>
@@ -4005,12 +3998,12 @@
       <c r="G88" s="1"/>
       <c r="H88" s="13"/>
       <c r="I88" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="50.45" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B89" s="25" t="s">
         <v>14</v>
@@ -4026,16 +4019,16 @@
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="50.45" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="B90" s="25" t="s">
         <v>14</v>
@@ -4053,12 +4046,12 @@
       <c r="G90" s="1"/>
       <c r="H90" s="14"/>
       <c r="I90" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="50.45" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="B91" s="25" t="s">
         <v>14</v>
@@ -4074,16 +4067,16 @@
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="H91" s="14"/>
       <c r="I91" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="50.45" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="B92" s="25" t="s">
         <v>14</v>
@@ -4099,16 +4092,16 @@
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H92" s="16"/>
       <c r="I92" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="50.45" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="B93" s="25" t="s">
         <v>17</v>
@@ -4124,16 +4117,16 @@
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="H93" s="14"/>
       <c r="I93" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="50.45" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="B94" s="25" t="s">
         <v>17</v>
@@ -4149,16 +4142,16 @@
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="H94" s="14"/>
       <c r="I94" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="50.45" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="B95" s="25" t="s">
         <v>14</v>
@@ -4173,17 +4166,17 @@
         <v>15</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="14"/>
       <c r="I95" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="50.45" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="B96" s="25" t="s">
         <v>14</v>
@@ -4199,14 +4192,14 @@
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="H96" s="15"/>
       <c r="I96" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="50.45" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>24</v>
       </c>
@@ -4223,17 +4216,17 @@
         <v>18</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="14"/>
       <c r="I97" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="50.45" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="B98" s="25" t="s">
         <v>17</v>
@@ -4249,25 +4242,25 @@
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="H98" s="22"/>
       <c r="I98" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="50.45" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C99" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>18</v>
@@ -4276,12 +4269,12 @@
       <c r="G99" s="1"/>
       <c r="H99" s="14"/>
       <c r="I99" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="50.45" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="B100" s="25" t="s">
         <v>14</v>
@@ -4299,12 +4292,12 @@
       <c r="G100" s="1"/>
       <c r="H100" s="13"/>
       <c r="I100" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="50.45" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="B101" s="25" t="s">
         <v>14</v>
@@ -4320,16 +4313,16 @@
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
-        <v>118</v>
+        <v>210</v>
       </c>
       <c r="H101" s="14"/>
       <c r="I101" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="50.45" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>17</v>
@@ -4347,12 +4340,12 @@
       <c r="G102" s="1"/>
       <c r="H102" s="14"/>
       <c r="I102" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="50.45" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="B103" s="25" t="s">
         <v>14</v>
@@ -4370,12 +4363,12 @@
       <c r="G103" s="1"/>
       <c r="H103" s="14"/>
       <c r="I103" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="50.45" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="B104" s="25" t="s">
         <v>14</v>
@@ -4391,16 +4384,16 @@
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="50.45" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="B105" s="25" t="s">
         <v>14</v>
@@ -4416,16 +4409,16 @@
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="50.45" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="B106" s="25" t="s">
         <v>17</v>
@@ -4441,16 +4434,16 @@
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H106" s="14"/>
       <c r="I106" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="50.45" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="B107" s="25" t="s">
         <v>17</v>
@@ -4466,16 +4459,16 @@
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>123</v>
+        <v>218</v>
       </c>
       <c r="H107" s="14"/>
       <c r="I107" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="50.45" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="B108" s="25" t="s">
         <v>17</v>
@@ -4493,12 +4486,12 @@
       <c r="G108" s="1"/>
       <c r="H108" s="14"/>
       <c r="I108" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="50.45" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="B109" s="25" t="s">
         <v>14</v>
@@ -4516,12 +4509,12 @@
       <c r="G109" s="1"/>
       <c r="H109" s="14"/>
       <c r="I109" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="58.9" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B110" s="25" t="s">
         <v>14</v>
@@ -4536,19 +4529,19 @@
         <v>15</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>124</v>
+        <v>222</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="50.45" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="B111" s="25" t="s">
         <v>17</v>
@@ -4564,16 +4557,16 @@
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="1" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="H111" s="14"/>
       <c r="I111" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="50.45" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="B112" s="25" t="s">
         <v>14</v>
@@ -4591,12 +4584,12 @@
       <c r="G112" s="1"/>
       <c r="H112" s="14"/>
       <c r="I112" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="50.45" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="B113" s="25" t="s">
         <v>14</v>
@@ -4616,12 +4609,12 @@
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="50.45" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>14</v>
@@ -4637,16 +4630,16 @@
       </c>
       <c r="F114" s="1"/>
       <c r="G114" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H114" s="14"/>
       <c r="I114" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="50.45" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="B115" s="25" t="s">
         <v>17</v>
@@ -4664,12 +4657,12 @@
       <c r="G115" s="1"/>
       <c r="H115" s="14"/>
       <c r="I115" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="50.45" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>17</v>
@@ -4685,16 +4678,16 @@
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>129</v>
+        <v>232</v>
       </c>
       <c r="H116" s="14"/>
       <c r="I116" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="50.45" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="B117" s="25" t="s">
         <v>14</v>
@@ -4712,12 +4705,12 @@
       <c r="G117" s="1"/>
       <c r="H117" s="14"/>
       <c r="I117" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="50.45" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="B118" s="25" t="s">
         <v>14</v>
@@ -4733,16 +4726,16 @@
       </c>
       <c r="F118" s="1"/>
       <c r="G118" s="1" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="H118" s="14"/>
       <c r="I118" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="50.45" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="B119" s="25" t="s">
         <v>14</v>
@@ -4758,16 +4751,16 @@
       </c>
       <c r="F119" s="1"/>
       <c r="G119" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="50.45" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="B120" s="25" t="s">
         <v>17</v>
@@ -4783,16 +4776,16 @@
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H120" s="14"/>
       <c r="I120" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="50.45" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B121" s="25" t="s">
         <v>17</v>
@@ -4808,16 +4801,16 @@
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="50.45" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="B122" s="25" t="s">
         <v>14</v>
@@ -4835,12 +4828,12 @@
       <c r="G122" s="1"/>
       <c r="H122" s="14"/>
       <c r="I122" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="50.45" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="B123" s="25" t="s">
         <v>14</v>
@@ -4856,16 +4849,16 @@
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1" t="s">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="85.15" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B124" s="25" t="s">
         <v>14</v>
@@ -4880,17 +4873,17 @@
         <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="G124" s="1"/>
       <c r="H124" s="14"/>
       <c r="I124" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="50.45" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="B125" s="25" t="s">
         <v>17</v>
@@ -4906,16 +4899,16 @@
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="1" t="s">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="H125" s="14"/>
       <c r="I125" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="50.45" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="B126" s="25" t="s">
         <v>17</v>
@@ -4935,12 +4928,12 @@
       </c>
       <c r="H126" s="14"/>
       <c r="I126" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="50.45" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="B127" s="25" t="s">
         <v>14</v>
@@ -4958,12 +4951,12 @@
       <c r="G127" s="1"/>
       <c r="H127" s="14"/>
       <c r="I127" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="50.45" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B128" s="25" t="s">
         <v>14</v>
@@ -4981,12 +4974,12 @@
       <c r="G128" s="1"/>
       <c r="H128" s="14"/>
       <c r="I128" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="50.45" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="B129" s="25" t="s">
         <v>14</v>
@@ -5004,12 +4997,12 @@
       <c r="G129" s="1"/>
       <c r="H129" s="14"/>
       <c r="I129" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="50.45" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="B130" s="25" t="s">
         <v>17</v>
@@ -5027,12 +5020,12 @@
       <c r="G130" s="1"/>
       <c r="H130" s="14"/>
       <c r="I130" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="50.45" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="B131" s="25" t="s">
         <v>17</v>
@@ -5050,12 +5043,12 @@
       <c r="G131" s="1"/>
       <c r="H131" s="14"/>
       <c r="I131" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="50.45" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="B132" s="25" t="s">
         <v>14</v>
@@ -5073,12 +5066,12 @@
       <c r="G132" s="1"/>
       <c r="H132" s="14"/>
       <c r="I132" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="50.45" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="B133" s="25" t="s">
         <v>14</v>
@@ -5096,12 +5089,12 @@
       <c r="G133" s="1"/>
       <c r="H133" s="14"/>
       <c r="I133" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="50.45" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="B134" s="25" t="s">
         <v>17</v>
@@ -5119,12 +5112,12 @@
       <c r="G134" s="1"/>
       <c r="H134" s="14"/>
       <c r="I134" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="50.45" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="B135" s="25" t="s">
         <v>17</v>
@@ -5142,7 +5135,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="14"/>
       <c r="I135" s="13" t="s">
-        <v>126</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5160,16 +5153,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDEF0F2C-2C42-44A9-B13E-0F50151640E7}">
   <dimension ref="A1:I135"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="126.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="5" width="27.6640625" customWidth="1"/>
-    <col min="6" max="8" width="50.6640625" customWidth="1"/>
-    <col min="9" max="9" width="24.44140625" customWidth="1"/>
+    <col min="1" max="1" width="126.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="5" width="27.7109375" customWidth="1"/>
+    <col min="6" max="8" width="50.7109375" customWidth="1"/>
+    <col min="9" max="9" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="42.6" customHeight="1" thickBot="1">
       <c r="A1" s="9" t="s">
         <v>4</v>
       </c>
@@ -5180,10 +5173,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>137</v>
+        <v>256</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>138</v>
+        <v>257</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>9</v>
@@ -5198,7 +5191,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="46.15" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -5219,7 +5212,7 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
     </row>
-    <row r="3" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="46.15" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -5244,7 +5237,7 @@
       </c>
       <c r="I3" s="13"/>
     </row>
-    <row r="4" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="46.15" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -5269,7 +5262,7 @@
       </c>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="46.15" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -5294,9 +5287,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="46.15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
@@ -5311,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="13"/>
@@ -5319,9 +5312,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="46.15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>14</v>
@@ -5342,9 +5335,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="46.15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>151</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>14</v>
@@ -5360,18 +5353,18 @@
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="46.15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>17</v>
@@ -5392,9 +5385,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="46.15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>14</v>
@@ -5415,9 +5408,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="46.15" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -5433,18 +5426,18 @@
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="46.15" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>14</v>
@@ -5460,18 +5453,18 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="46.15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>17</v>
@@ -5487,18 +5480,18 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="46.15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>17</v>
@@ -5514,18 +5507,18 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="46.15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>17</v>
@@ -5546,9 +5539,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="106.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="106.9" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>14</v>
@@ -5563,7 +5556,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="14"/>
@@ -5571,9 +5564,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="46.15" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
@@ -5588,17 +5581,17 @@
         <v>15</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="14"/>
       <c r="I17" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="43.15">
       <c r="A18" s="1" t="s">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>14</v>
@@ -5613,17 +5606,17 @@
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="18"/>
       <c r="I18" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="86.45">
       <c r="A19" s="1" t="s">
-        <v>162</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>14</v>
@@ -5639,18 +5632,18 @@
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="1" t="s">
-        <v>44</v>
+        <v>258</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="72" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>14</v>
@@ -5666,16 +5659,16 @@
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="1" t="s">
-        <v>45</v>
+        <v>260</v>
       </c>
       <c r="H20" s="18"/>
       <c r="I20" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="46.15" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>17</v>
@@ -5690,17 +5683,17 @@
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="18"/>
       <c r="I21" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="46.15" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>17</v>
@@ -5716,18 +5709,18 @@
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="46.15" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>17</v>
@@ -5745,12 +5738,12 @@
       <c r="G23" s="1"/>
       <c r="H23" s="14"/>
       <c r="I23" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="46.15" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>17</v>
@@ -5766,18 +5759,18 @@
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="46.15" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>17</v>
@@ -5795,12 +5788,12 @@
       <c r="G25" s="1"/>
       <c r="H25" s="14"/>
       <c r="I25" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="46.15" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>14</v>
@@ -5818,12 +5811,12 @@
       <c r="G26" s="1"/>
       <c r="H26" s="14"/>
       <c r="I26" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="46.15" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>17</v>
@@ -5841,12 +5834,12 @@
       <c r="G27" s="23"/>
       <c r="H27" s="19"/>
       <c r="I27" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="46.15" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>14</v>
@@ -5861,17 +5854,17 @@
         <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="14"/>
       <c r="I28" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="46.15" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>17</v>
@@ -5886,17 +5879,17 @@
         <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="14"/>
       <c r="I29" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="46.15" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>17</v>
@@ -5911,17 +5904,17 @@
         <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="14"/>
       <c r="I30" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="46.15" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>14</v>
@@ -5936,17 +5929,17 @@
         <v>15</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="14"/>
       <c r="I31" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="46.15" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>17</v>
@@ -5961,17 +5954,17 @@
         <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="14"/>
       <c r="I32" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="46.15" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>14</v>
@@ -5986,17 +5979,17 @@
         <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="14"/>
       <c r="I33" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="46.15" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>17</v>
@@ -6011,17 +6004,17 @@
         <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="14"/>
       <c r="I34" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="164.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="164.45" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>17</v>
@@ -6036,42 +6029,42 @@
         <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="14"/>
       <c r="I35" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="46.15" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G36" s="23"/>
       <c r="H36" s="14"/>
       <c r="I36" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="46.15" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>14</v>
@@ -6089,12 +6082,12 @@
       <c r="G37" s="1"/>
       <c r="H37" s="14"/>
       <c r="I37" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="46.15" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>181</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>14</v>
@@ -6112,12 +6105,12 @@
       <c r="G38" s="1"/>
       <c r="H38" s="14"/>
       <c r="I38" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="46.15" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>17</v>
@@ -6135,12 +6128,12 @@
       <c r="G39" s="1"/>
       <c r="H39" s="14"/>
       <c r="I39" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="46.15" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>183</v>
+        <v>95</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>17</v>
@@ -6155,17 +6148,17 @@
         <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="20"/>
       <c r="I40" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="46.15" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>17</v>
@@ -6181,16 +6174,16 @@
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>139</v>
+        <v>261</v>
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="46.15" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>14</v>
@@ -6208,12 +6201,12 @@
       <c r="G42" s="1"/>
       <c r="H42" s="14"/>
       <c r="I42" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="46.15" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>17</v>
@@ -6229,16 +6222,16 @@
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="46.15" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>14</v>
@@ -6254,18 +6247,18 @@
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="H44" s="14" t="s">
         <v>23</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="46.15" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>14</v>
@@ -6283,12 +6276,12 @@
       <c r="G45" s="1"/>
       <c r="H45" s="14"/>
       <c r="I45" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="46.15" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>280</v>
+        <v>104</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>14</v>
@@ -6304,18 +6297,18 @@
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="46.15" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>14</v>
@@ -6331,18 +6324,18 @@
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="46.15" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>17</v>
@@ -6358,18 +6351,18 @@
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="46.15" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>283</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>17</v>
@@ -6387,12 +6380,12 @@
       <c r="G49" s="1"/>
       <c r="H49" s="14"/>
       <c r="I49" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="46.15" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>17</v>
@@ -6410,37 +6403,37 @@
       <c r="G50" s="1"/>
       <c r="H50" s="14"/>
       <c r="I50" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="88.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="88.9" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="14"/>
       <c r="I51" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="46.15" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>14</v>
@@ -6458,12 +6451,12 @@
       <c r="G52" s="1"/>
       <c r="H52" s="14"/>
       <c r="I52" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="46.15" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>14</v>
@@ -6479,18 +6472,18 @@
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="46.15" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>14</v>
@@ -6512,12 +6505,12 @@
         <v>23</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="46.15" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>17</v>
@@ -6535,12 +6528,12 @@
       <c r="G55" s="1"/>
       <c r="H55" s="15"/>
       <c r="I55" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="46.15" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>14</v>
@@ -6556,18 +6549,18 @@
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="46.15" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>17</v>
@@ -6585,12 +6578,12 @@
       <c r="G57" s="1"/>
       <c r="H57" s="13"/>
       <c r="I57" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="46.15" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>196</v>
+        <v>127</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>17</v>
@@ -6606,18 +6599,18 @@
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="46.15" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>17</v>
@@ -6633,18 +6626,18 @@
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="46.15" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>17</v>
@@ -6660,18 +6653,18 @@
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="46.15" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>17</v>
@@ -6687,18 +6680,18 @@
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="46.15" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>14</v>
@@ -6713,44 +6706,44 @@
         <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="14"/>
       <c r="I62" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="46.15" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>15</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="46.15" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>14</v>
@@ -6766,18 +6759,18 @@
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="46.15" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>14</v>
@@ -6793,18 +6786,18 @@
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1" t="s">
-        <v>144</v>
+        <v>266</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="46.15" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>14</v>
@@ -6819,17 +6812,17 @@
         <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="14"/>
       <c r="I66" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="46.15" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>17</v>
@@ -6845,18 +6838,18 @@
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="46.15" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>14</v>
@@ -6878,12 +6871,12 @@
         <v>23</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="46.15" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>14</v>
@@ -6901,12 +6894,12 @@
       <c r="G69" s="1"/>
       <c r="H69" s="17"/>
       <c r="I69" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="46.15" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>14</v>
@@ -6922,18 +6915,18 @@
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
-        <v>145</v>
+        <v>267</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="46.15" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>209</v>
+        <v>157</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>14</v>
@@ -6951,12 +6944,12 @@
       <c r="G71" s="1"/>
       <c r="H71" s="15"/>
       <c r="I71" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="46.15" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>14</v>
@@ -6972,18 +6965,18 @@
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="46.15" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>14</v>
@@ -6999,18 +6992,18 @@
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="46.15" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>17</v>
@@ -7026,18 +7019,18 @@
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="46.15" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>17</v>
@@ -7053,18 +7046,18 @@
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="H75" s="14" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="46.15" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>14</v>
@@ -7082,12 +7075,12 @@
       <c r="G76" s="1"/>
       <c r="H76" s="16"/>
       <c r="I76" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="46.15" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>240</v>
+        <v>167</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>14</v>
@@ -7103,18 +7096,18 @@
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="H77" s="14" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="46.15" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>14</v>
@@ -7132,12 +7125,12 @@
       <c r="G78" s="1"/>
       <c r="H78" s="14"/>
       <c r="I78" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="46.15" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>14</v>
@@ -7153,18 +7146,18 @@
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="H79" s="14" t="s">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="46.15" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>17</v>
@@ -7180,18 +7173,18 @@
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1" t="s">
-        <v>146</v>
+        <v>268</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="46.15" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>17</v>
@@ -7209,12 +7202,12 @@
       <c r="G81" s="1"/>
       <c r="H81" s="14"/>
       <c r="I81" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="46.15" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>17</v>
@@ -7229,17 +7222,17 @@
         <v>15</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="22"/>
       <c r="I82" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="46.15" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>14</v>
@@ -7255,18 +7248,18 @@
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H83" s="14" t="s">
-        <v>102</v>
+        <v>269</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="46.15" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>279</v>
+        <v>182</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>14</v>
@@ -7282,18 +7275,18 @@
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="46.15" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>14</v>
@@ -7308,17 +7301,17 @@
         <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="14"/>
       <c r="I85" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="46.15" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>17</v>
@@ -7334,18 +7327,18 @@
       </c>
       <c r="F86" s="1"/>
       <c r="G86" s="1" t="s">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="H86" s="14" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="46.15" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>14</v>
@@ -7361,18 +7354,18 @@
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="H87" s="14" t="s">
         <v>23</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="46.15" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>14</v>
@@ -7390,12 +7383,12 @@
       <c r="G88" s="1"/>
       <c r="H88" s="13"/>
       <c r="I88" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="46.15" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>14</v>
@@ -7411,18 +7404,18 @@
       </c>
       <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>107</v>
+        <v>270</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="46.15" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>14</v>
@@ -7440,12 +7433,12 @@
       <c r="G90" s="1"/>
       <c r="H90" s="14"/>
       <c r="I90" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="46.15" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>14</v>
@@ -7461,18 +7454,18 @@
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="46.15" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>14</v>
@@ -7488,18 +7481,18 @@
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H92" s="16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="46.15" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>17</v>
@@ -7515,18 +7508,18 @@
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="H93" s="14" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="46.15" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>17</v>
@@ -7542,18 +7535,18 @@
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="46.15" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>14</v>
@@ -7568,17 +7561,17 @@
         <v>15</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="G95" s="1"/>
       <c r="H95" s="14"/>
       <c r="I95" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="46.15" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>14</v>
@@ -7594,16 +7587,16 @@
       </c>
       <c r="F96" s="1"/>
       <c r="G96" s="1" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="H96" s="15" t="s">
-        <v>114</v>
+        <v>272</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="46.15" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>24</v>
       </c>
@@ -7620,17 +7613,17 @@
         <v>15</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="14"/>
       <c r="I97" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="46.15" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>17</v>
@@ -7646,27 +7639,27 @@
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="H98" s="22" t="s">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="46.15" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>15</v>
@@ -7675,12 +7668,12 @@
       <c r="G99" s="1"/>
       <c r="H99" s="14"/>
       <c r="I99" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="46.15" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>14</v>
@@ -7698,12 +7691,12 @@
       <c r="G100" s="1"/>
       <c r="H100" s="13"/>
       <c r="I100" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="46.15" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>14</v>
@@ -7719,18 +7712,18 @@
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
-        <v>147</v>
+        <v>274</v>
       </c>
       <c r="H101" s="14" t="s">
-        <v>119</v>
+        <v>275</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="46.15" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>17</v>
@@ -7748,12 +7741,12 @@
       <c r="G102" s="1"/>
       <c r="H102" s="14"/>
       <c r="I102" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="46.15" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>14</v>
@@ -7771,12 +7764,12 @@
       <c r="G103" s="1"/>
       <c r="H103" s="14"/>
       <c r="I103" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="46.15" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>14</v>
@@ -7792,18 +7785,18 @@
       </c>
       <c r="F104" s="1"/>
       <c r="G104" s="1" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="H104" s="14" t="s">
-        <v>121</v>
+        <v>276</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="46.15" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>14</v>
@@ -7819,18 +7812,18 @@
       </c>
       <c r="F105" s="1"/>
       <c r="G105" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H105" s="14" t="s">
-        <v>122</v>
+        <v>277</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="46.15" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>17</v>
@@ -7846,18 +7839,18 @@
       </c>
       <c r="F106" s="1"/>
       <c r="G106" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H106" s="14" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="46.15" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>17</v>
@@ -7873,18 +7866,18 @@
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1" t="s">
-        <v>148</v>
+        <v>278</v>
       </c>
       <c r="H107" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="46.15" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>17</v>
@@ -7902,12 +7895,12 @@
       <c r="G108" s="1"/>
       <c r="H108" s="14"/>
       <c r="I108" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="46.15" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>14</v>
@@ -7925,12 +7918,12 @@
       <c r="G109" s="1"/>
       <c r="H109" s="14"/>
       <c r="I109" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="80.45" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>14</v>
@@ -7945,19 +7938,19 @@
         <v>15</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>124</v>
+        <v>222</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="46.15" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>17</v>
@@ -7973,18 +7966,18 @@
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="1" t="s">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="H111" s="14" t="s">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="46.15" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>14</v>
@@ -8002,12 +7995,12 @@
       <c r="G112" s="1"/>
       <c r="H112" s="14"/>
       <c r="I112" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="46.15" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>14</v>
@@ -8029,12 +8022,12 @@
         <v>23</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="46.15" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>14</v>
@@ -8050,18 +8043,18 @@
       </c>
       <c r="F114" s="1"/>
       <c r="G114" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H114" s="14" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="46.15" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>17</v>
@@ -8079,12 +8072,12 @@
       <c r="G115" s="1"/>
       <c r="H115" s="14"/>
       <c r="I115" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="46.15" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>17</v>
@@ -8100,18 +8093,18 @@
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>129</v>
+        <v>232</v>
       </c>
       <c r="H116" s="14" t="s">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="46.15" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>14</v>
@@ -8129,12 +8122,12 @@
       <c r="G117" s="1"/>
       <c r="H117" s="14"/>
       <c r="I117" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="46.15" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>14</v>
@@ -8150,18 +8143,18 @@
       </c>
       <c r="F118" s="1"/>
       <c r="G118" s="1" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="H118" s="14" t="s">
-        <v>121</v>
+        <v>276</v>
       </c>
       <c r="I118" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="46.15" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>14</v>
@@ -8177,18 +8170,18 @@
       </c>
       <c r="F119" s="1"/>
       <c r="G119" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H119" s="14" t="s">
-        <v>122</v>
+        <v>277</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="46.15" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>17</v>
@@ -8204,18 +8197,18 @@
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H120" s="14" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I120" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="46.15" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>17</v>
@@ -8231,18 +8224,18 @@
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="H121" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="46.15" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>239</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>14</v>
@@ -8260,12 +8253,12 @@
       <c r="G122" s="1"/>
       <c r="H122" s="14"/>
       <c r="I122" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="46.15" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>14</v>
@@ -8281,18 +8274,18 @@
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1" t="s">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="H123" s="14" t="s">
-        <v>133</v>
+        <v>281</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="100.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="100.15" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>14</v>
@@ -8307,17 +8300,17 @@
         <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="G124" s="1"/>
       <c r="H124" s="14"/>
       <c r="I124" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="46.15" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>17</v>
@@ -8333,18 +8326,18 @@
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="1" t="s">
-        <v>135</v>
+        <v>245</v>
       </c>
       <c r="H125" s="14" t="s">
-        <v>136</v>
+        <v>282</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="46.15" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>17</v>
@@ -8366,12 +8359,12 @@
         <v>23</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="46.15" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>14</v>
@@ -8389,12 +8382,12 @@
       <c r="G127" s="23"/>
       <c r="H127" s="14"/>
       <c r="I127" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="46.15" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>14</v>
@@ -8412,12 +8405,12 @@
       <c r="G128" s="1"/>
       <c r="H128" s="14"/>
       <c r="I128" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="46.15" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>14</v>
@@ -8435,12 +8428,12 @@
       <c r="G129" s="1"/>
       <c r="H129" s="14"/>
       <c r="I129" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="46.15" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>17</v>
@@ -8458,12 +8451,12 @@
       <c r="G130" s="1"/>
       <c r="H130" s="14"/>
       <c r="I130" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="46.15" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>17</v>
@@ -8481,12 +8474,12 @@
       <c r="G131" s="23"/>
       <c r="H131" s="14"/>
       <c r="I131" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="46.15" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>14</v>
@@ -8504,12 +8497,12 @@
       <c r="G132" s="1"/>
       <c r="H132" s="14"/>
       <c r="I132" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="46.15" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>14</v>
@@ -8527,12 +8520,12 @@
       <c r="G133" s="1"/>
       <c r="H133" s="14"/>
       <c r="I133" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="46.15" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>17</v>
@@ -8550,12 +8543,12 @@
       <c r="G134" s="1"/>
       <c r="H134" s="14"/>
       <c r="I134" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="46.15" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>17</v>
@@ -8573,7 +8566,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="14"/>
       <c r="I135" s="13" t="s">
-        <v>126</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -8588,20 +8581,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d04b37e-0497-498c-96f6-8855740e5edb">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010099D50BAF6148C0469FC2106F96A8440B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0ded3a6aadbdf34d96c7fc30e5856767">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3d04b37e-0497-498c-96f6-8855740e5edb" xmlns:ns3="14722739-9480-433a-8c7c-4ec5d8a77ba5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f351b1b6c8daa9a12afc7a7c24e3e10f" ns2:_="" ns3:_="">
-    <xsd:import namespace="3d04b37e-0497-498c-96f6-8855740e5edb"/>
-    <xsd:import namespace="14722739-9480-433a-8c7c-4ec5d8a77ba5"/>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
+    <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <xsd:import namespace="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -8610,16 +8614,22 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:UserStoryALM" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -8627,7 +8637,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3d04b37e-0497-498c-96f6-8855740e5edb" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1e76d14e-d0ce-457c-8343-9b55836d9ead" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -8640,55 +8650,96 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="11" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="33ef62f9-2e07-484b-bd79-00aec90129fe" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="15" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="16" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6d165d17-9b79-46c3-82b9-c927e733c429" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="17" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="UserStoryALM" ma:index="25" nillable="true" ma:displayName="UserStory ALM" ma:format="Dropdown" ma:internalName="UserStoryALM">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="137048 - Stesura checklist RAP"/>
+          <xsd:enumeration value="137049 - Sviluppo testcase RAP"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14722739-9480-433a-8c7c-4ec5d8a77ba5" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a56712a3-8dfd-4688-917a-22f0cf513b89" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c488629b-a647-4465-8bb2-a216a95770f0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a56712a3-8dfd-4688-917a-22f0cf513b89">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -8707,7 +8758,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -8814,55 +8865,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0512D7E3-50F2-444E-9ED7-B3EF961BAB5C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="3d04b37e-0497-498c-96f6-8855740e5edb"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="14722739-9480-433a-8c7c-4ec5d8a77ba5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7546A8C9-5E58-4696-BB95-DC050D754164}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F360291-6422-41C3-9DF0-CA2A088B840B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3d04b37e-0497-498c-96f6-8855740e5edb"/>
-    <ds:schemaRef ds:uri="14722739-9480-433a-8c7c-4ec5d8a77ba5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0512D7E3-50F2-444E-9ED7-B3EF961BAB5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7546A8C9-5E58-4696-BB95-DC050D754164}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0702AFFB-38EE-4512-94F7-4C8A52E15253}"/>
 </file>